--- a/artfynd/A 41412-2022 artfynd.xlsx
+++ b/artfynd/A 41412-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41412-2022 artfynd.xlsx
+++ b/artfynd/A 41412-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68303573</v>
+        <v>68303559</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802386.846957901</v>
+        <v>802373</v>
       </c>
       <c r="R2" t="n">
-        <v>7162184.420617844</v>
+        <v>7162175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,19 +749,9 @@
           <t>2015-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68303633</v>
+        <v>68303629</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802369.7602999993</v>
+        <v>802365</v>
       </c>
       <c r="R3" t="n">
-        <v>7162133.201666848</v>
+        <v>7162225</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2015-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68303559</v>
+        <v>68303631</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802372.974557464</v>
+        <v>802275</v>
       </c>
       <c r="R4" t="n">
-        <v>7162175.221965946</v>
+        <v>7162265</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +957,9 @@
           <t>2015-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68303631</v>
+        <v>68303633</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802274.894586853</v>
+        <v>802370</v>
       </c>
       <c r="R5" t="n">
-        <v>7162264.938731117</v>
+        <v>7162133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1061,9 @@
           <t>2015-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,16 +1094,11 @@
         <v>68303541</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1197,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802306.2499271443</v>
+        <v>802306</v>
       </c>
       <c r="R6" t="n">
-        <v>7162146.432641409</v>
+        <v>7162146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,19 +1165,9 @@
           <t>2015-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,6 +1192,244 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>68303573</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rävelsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>802387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7162184</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-09-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-09-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>68303586</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rävelsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>802427</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7162174</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-09-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-09-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>gammelskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>färska hackspår</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies # färska hackspår</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41412-2022 artfynd.xlsx
+++ b/artfynd/A 41412-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303559</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303633</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303541</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303573</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,8 +1465,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68303586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>